--- a/lcr_analyses/clustering/carriers/FLPS/cluster_summaries_hierarchical.xlsx
+++ b/lcr_analyses/clustering/carriers/FLPS/cluster_summaries_hierarchical.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4330,4 +4334,5546 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5570680628272251</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.7575187969924813</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3374083129584352</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1100244498777506</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.09535452322738384</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.7481662591687042</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.2518796992481203</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1124694376528117</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3789731051344744</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1540342298288508</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.3022026431718062</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1532</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1499537322640346</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.11111111111111</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.260443864229765</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3074412532637076</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4523498694516971</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1475195822454308</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.466710182767624</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.06723237597911227</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.05287206266318538</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.09399477806788512</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2689295039164491</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.314621409921671</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3890339425587467</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.05352480417754569</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.01109660574412533</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2108355091383812</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3988250652741515</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.03198433420365535</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.097911227154047</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.4654046997389034</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.0097911227154047</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.01436031331592689</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.003263707571801566</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.04503916449086162</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1462140992167102</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5657230196703881</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5166666666666667</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1860774818401937</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.6622499122499123</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1435185185185185</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1005952380952381</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2958754208754208</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.02484567901234567</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>581</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>319</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>143</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>118</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>107</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>106</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>82</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3754601226993865</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32.08333333333334</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1441441441441441</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5045045045045045</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6576576576576577</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8198198198198198</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1261261261261261</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3873873873873874</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5315315315315315</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5675675675675675</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6396396396396397</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9819819819819819</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5855855855855856</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1531531531531531</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.8738738738738738</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.03603603603603604</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.07207207207207207</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.01801801801801802</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1171171171171171</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3693693693693694</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6095238095238096</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.4241758241758242</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.160958904109589</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05691056910569105</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1557177615571776</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.161038961038961</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3212669683257919</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.003597122302158267</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1856287425149701</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1686305288604344</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5114645858343337</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5010204081632653</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1940476190476191</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.101844070961718</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6293083900226757</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.04818594104308389</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.03301320528211284</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.07414965986394557</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.006302521008403364</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3078514739229025</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3926543571965253</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8409090909090909</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6136363636363636</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4772727272727273</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.2045454545454546</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5402476780185759</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4710847855323776</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1498739711360443</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.06718281718281718</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.739281045751634</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1375675675675676</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0771712158808933</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.2286036036036036</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.04531266167695651</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.3028904022806462</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2911777698310861</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30.02197802197802</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5906948145111703</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4503228120516499</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2205882352941176</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1327116212338594</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5732219717155155</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1120106579217053</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1150594384095101</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2270700963312154</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.003048780487804875</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.0977146956343513</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5767123287671233</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60.14285714285715</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3111638954869358</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.6722090261282661</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2921615201900237</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.02850356294536817</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6199524940617577</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.08551068883610451</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1021377672209026</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.1876484560570071</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.0166270783847981</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2992874109263658</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5570680628272251</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.7575187969924813</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3374083129584352</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1100244498777506</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.09535452322738384</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.7481662591687042</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.2518796992481203</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1124694376528117</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3789731051344744</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1540342298288508</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.3022026431718062</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1532</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1499537322640346</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.11111111111111</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.260443864229765</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3074412532637076</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4523498694516971</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1475195822454308</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.466710182767624</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.06723237597911227</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.05287206266318538</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.09399477806788512</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2689295039164491</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.314621409921671</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3890339425587467</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.05352480417754569</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.01109660574412533</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2108355091383812</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3988250652741515</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.03198433420365535</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.097911227154047</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.4654046997389034</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.0097911227154047</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.01436031331592689</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.003263707571801566</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.04503916449086162</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1462140992167102</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5657230196703881</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5166666666666667</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1860774818401937</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.6622499122499123</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1435185185185185</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1005952380952381</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2958754208754208</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.02484567901234567</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>581</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>319</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>143</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>118</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>107</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>106</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>82</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3754601226993865</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32.08333333333334</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1441441441441441</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5045045045045045</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6576576576576577</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8198198198198198</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1261261261261261</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3873873873873874</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5315315315315315</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5675675675675675</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6396396396396397</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9819819819819819</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5855855855855856</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1531531531531531</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.8738738738738738</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.03603603603603604</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.07207207207207207</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.01801801801801802</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1171171171171171</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3693693693693694</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6095238095238096</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.4241758241758242</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.160958904109589</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05691056910569105</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1557177615571776</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.161038961038961</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3212669683257919</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.003597122302158267</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1856287425149701</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1686305288604344</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5114645858343337</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5010204081632653</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1940476190476191</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.101844070961718</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6293083900226757</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.04818594104308389</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.03301320528211284</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.07414965986394557</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.006302521008403364</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3078514739229025</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6615384615384615</v>
+      </c>
+      <c r="E6" t="n">
+        <v>46</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.542713567839196</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4351145038167939</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1374045801526718</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.09448818897637795</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.748062015503876</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1464646464646465</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.08778625954198473</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.2636363636363636</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.05434782608695652</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.3661417322834646</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.299660441426146</v>
+      </c>
+      <c r="E7" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5380116959064327</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4747474747474748</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.152046783625731</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.05732484076433121</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7282608695652174</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2072072072072072</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.04430379746835443</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2911777698310861</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30.02197802197802</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5906948145111703</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4503228120516499</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2205882352941176</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1327116212338594</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5732219717155155</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1120106579217053</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1150594384095101</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2270700963312154</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.003048780487804875</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.0977146956343513</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5767123287671233</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60.14285714285715</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.3111638954869358</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.6722090261282661</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.2921615201900237</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.02850356294536817</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.6199524940617577</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.08551068883610451</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1021377672209026</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.1876484560570071</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.0166270783847981</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2992874109263658</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5570680628272251</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.7575187969924813</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3374083129584352</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1100244498777506</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.09535452322738384</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.7481662591687042</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.2518796992481203</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1124694376528117</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3789731051344744</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1540342298288508</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.3022026431718062</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>169</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1515789473684211</v>
+      </c>
+      <c r="E3" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6213017751479289</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5976331360946746</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4970414201183432</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6686390532544378</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02366863905325444</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.03550295857988166</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.08875739644970414</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6272189349112426</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5857988165680473</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8165680473372781</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1005917159763314</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.005917159763313609</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3905325443786982</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.591715976331361</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.08284023668639054</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1834319526627219</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.591715976331361</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.02366863905325444</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.02958579881656805</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.01183431952662722</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.05917159763313609</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4023668639053254</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6070038910505836</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1968911917098446</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.05645161290322582</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1774193548387097</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1658986175115207</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.005291005291005291</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1186440677966102</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1363</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1499074645280691</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21.625</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2157006603081438</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2714600146735143</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4468085106382979</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1085840058694057</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4416727806309611</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07263389581804842</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.05502567865003669</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0946441672780631</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2245047688921497</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.280997798972854</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3360234776228907</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04768892149669846</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.01173881144534116</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1885546588407924</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.3749082905355833</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.02567865003668379</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.08730741012472487</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.4497432134996331</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.008070432868672046</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01247248716067498</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.002201027146001467</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.04328686720469552</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1144534115920763</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5564516129032258</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5166666666666667</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1853658536585366</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0641025641025641</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.08860759493670886</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2765957446808511</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.02757352941176471</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>530</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>274</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>64</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>92</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>132</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3754601226993865</v>
+      </c>
+      <c r="E5" t="n">
+        <v>32.08333333333334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1441441441441441</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5045045045045045</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6576576576576577</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8198198198198198</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1261261261261261</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3873873873873874</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5315315315315315</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5675675675675675</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6396396396396397</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.9819819819819819</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5855855855855856</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1531531531531531</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.8738738738738738</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.03603603603603604</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.07207207207207207</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.01801801801801802</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1171171171171171</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.3693693693693694</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6095238095238096</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4241758241758242</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.160958904109589</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.05691056910569105</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1557177615571776</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.161038961038961</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.3212669683257919</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.003597122302158267</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1856287425149701</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1686305288604344</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5114645858343337</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5010204081632653</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1940476190476191</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.101844070961718</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6293083900226757</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.04818594104308389</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.03301320528211284</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.07414965986394557</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.006302521008403364</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.3078514739229025</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6615384615384615</v>
+      </c>
+      <c r="E7" t="n">
+        <v>46</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.542713567839196</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4351145038167939</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1374045801526718</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.09448818897637795</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.748062015503876</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1464646464646465</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.08778625954198473</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2636363636363636</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.05434782608695652</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.3661417322834646</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>33</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.299660441426146</v>
+      </c>
+      <c r="E8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5380116959064327</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4747474747474748</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.152046783625731</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.05732484076433121</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7282608695652174</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2072072072072072</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.04430379746835443</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2911777698310861</v>
+      </c>
+      <c r="E9" t="n">
+        <v>30.02197802197802</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5906948145111703</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.4503228120516499</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.2205882352941176</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1327116212338594</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.5732219717155155</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1120106579217053</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1150594384095101</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.2270700963312154</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.003048780487804875</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0977146956343513</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5767123287671233</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60.14285714285715</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.3111638954869358</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6722090261282661</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.2921615201900237</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.02850356294536817</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.6199524940617577</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.08551068883610451</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1021377672209026</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.1876484560570071</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.0166270783847981</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.2992874109263658</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5570680628272251</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.7575187969924813</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3374083129584352</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1100244498777506</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.09535452322738384</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.7481662591687042</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.2518796992481203</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1124694376528117</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3789731051344744</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1540342298288508</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.3022026431718062</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>169</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1515789473684211</v>
+      </c>
+      <c r="E3" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6213017751479289</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5976331360946746</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4970414201183432</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6686390532544378</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02366863905325444</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.03550295857988166</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.08875739644970414</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6272189349112426</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5857988165680473</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8165680473372781</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1005917159763314</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.005917159763313609</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3905325443786982</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.591715976331361</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.08284023668639054</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1834319526627219</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.591715976331361</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.02366863905325444</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.02958579881656805</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.01183431952662722</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.05917159763313609</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4023668639053254</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6070038910505836</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1968911917098446</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.05645161290322582</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1774193548387097</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1658986175115207</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.005291005291005291</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1186440677966102</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>81</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04081632653061224</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3950617283950617</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3580246913580247</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.08641975308641975</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.08641975308641975</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1234567901234568</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.08641975308641975</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.08641975308641975</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04938271604938271</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8271604938271605</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.06172839506172839</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1604938271604938</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1358024691358025</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01234567901234568</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.01234567901234568</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.04938271604938271</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.07692307692307694</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1282</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1611740074441687</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2043681747269891</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2745709828393136</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.452418096723869</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.109984399375975</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4641185647425897</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.07722308892355695</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.05850234009360374</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1006240249609984</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2308892355694228</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2932917316692668</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3517940717628705</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.04758190327613104</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0124804992199688</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1482059282371295</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3946957878315133</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0171606864274571</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.09282371294851795</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4695787831513261</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.008580343213728549</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0124804992199688</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.0015600624024961</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04602184087363494</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1185647425897036</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5643457333985968</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5076923076923077</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.06326908821349148</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6744186046511628</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1375358617863111</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.09245014245014245</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.286019536019536</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.02855735254145148</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>516</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>252</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>62</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>87</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>114</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3754601226993865</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.08333333333334</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1441441441441441</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5045045045045045</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6576576576576577</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8198198198198198</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1261261261261261</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3873873873873874</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5315315315315315</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5675675675675675</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6396396396396397</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9819819819819819</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5855855855855856</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1531531531531531</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.8738738738738738</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.03603603603603604</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.07207207207207207</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.01801801801801802</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1171171171171171</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.3693693693693694</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6095238095238096</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4241758241758242</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.160958904109589</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.05691056910569105</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1557177615571776</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.161038961038961</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3212669683257919</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.003597122302158267</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1856287425149701</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1686305288604344</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5114645858343337</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5010204081632653</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1940476190476191</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.101844070961718</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.6293083900226757</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.04818594104308389</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.03301320528211284</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.07414965986394557</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.006302521008403364</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.3078514739229025</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6615384615384615</v>
+      </c>
+      <c r="E8" t="n">
+        <v>46</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.542713567839196</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4351145038167939</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1374045801526718</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.09448818897637795</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.748062015503876</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1464646464646465</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.08778625954198473</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2636363636363636</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.05434782608695652</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.3661417322834646</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>33</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.299660441426146</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1515151515151515</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5380116959064327</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.4747474747474748</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.152046783625731</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.05732484076433121</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7282608695652174</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.2072072072072072</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.04430379746835443</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2911777698310861</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30.02197802197802</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5906948145111703</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.4503228120516499</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.2205882352941176</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.1327116212338594</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5732219717155155</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1120106579217053</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1150594384095101</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.2270700963312154</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.003048780487804875</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.0977146956343513</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5767123287671233</v>
+      </c>
+      <c r="E11" t="n">
+        <v>60.14285714285715</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.3111638954869358</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.6722090261282661</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.2921615201900237</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.02850356294536817</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.6199524940617577</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.08551068883610451</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1021377672209026</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.1876484560570071</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.0166270783847981</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.2992874109263658</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>